--- a/seed_nao_lancados.xlsx
+++ b/seed_nao_lancados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB349"/>
+  <dimension ref="A1:AB413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31904,6 +31904,6098 @@
       </c>
       <c r="AB349" t="inlineStr"/>
     </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2026062612415954.0</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>10</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>08.325.415/0001-47</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>UNILESTE</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>CONSÓRCIO UNILESTE</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>UNILESTE</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>ITAQUAQUECETUBA</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>Itaquaquecetuba</t>
+        </is>
+      </c>
+      <c r="P350" t="n">
+        <v>3523107</v>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>SUZANO</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>Suzano</t>
+        </is>
+      </c>
+      <c r="S350" t="n">
+        <v>3552502</v>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>MUDANÇA DE TABELA DE HORÁRIO</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr"/>
+      <c r="W350" t="inlineStr"/>
+      <c r="X350" t="inlineStr"/>
+      <c r="Y350" t="inlineStr"/>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>2026071409132659.0</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>20</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr"/>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr"/>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr"/>
+      <c r="O351" t="inlineStr"/>
+      <c r="P351" t="inlineStr"/>
+      <c r="Q351" t="inlineStr"/>
+      <c r="R351" t="inlineStr"/>
+      <c r="S351" t="inlineStr"/>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>SOLICITAÇÃO DE INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>2026-07-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="W351" t="inlineStr"/>
+      <c r="X351" t="inlineStr"/>
+      <c r="Y351" t="inlineStr"/>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>CARTÃO DE VISTORIA</t>
+        </is>
+      </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>2026072813413870.0</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>20</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr"/>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr"/>
+      <c r="O352" t="inlineStr"/>
+      <c r="P352" t="inlineStr"/>
+      <c r="Q352" t="inlineStr"/>
+      <c r="R352" t="inlineStr"/>
+      <c r="S352" t="inlineStr"/>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>SOLICITAÇÃO DE INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>2026-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr"/>
+      <c r="X352" t="inlineStr"/>
+      <c r="Y352" t="inlineStr"/>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>CARTÃO DE VISTORIA</t>
+        </is>
+      </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2026072711215113.0</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>20</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr"/>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>SOROCABA</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>Sorocaba</t>
+        </is>
+      </c>
+      <c r="P353" t="n">
+        <v>3552205</v>
+      </c>
+      <c r="Q353" t="inlineStr"/>
+      <c r="R353" t="inlineStr"/>
+      <c r="S353" t="inlineStr"/>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>SOLICITAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>2026-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr"/>
+      <c r="X353" t="inlineStr"/>
+      <c r="Y353" t="inlineStr"/>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>2026072910145450.0</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>20</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>SOROCABA</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>Sorocaba</t>
+        </is>
+      </c>
+      <c r="P354" t="n">
+        <v>3552205</v>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>VOTORANTIM</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>Votorantim</t>
+        </is>
+      </c>
+      <c r="S354" t="n">
+        <v>3557006</v>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>SOLICITAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>2026-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr"/>
+      <c r="X354" t="inlineStr"/>
+      <c r="Y354" t="inlineStr"/>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>2026073010073828.0</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>20</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>SÃO PAULO</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="P355" t="n">
+        <v>3550308</v>
+      </c>
+      <c r="Q355" t="inlineStr"/>
+      <c r="R355" t="inlineStr"/>
+      <c r="S355" t="inlineStr"/>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>SOLICITAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>2026-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="W355" t="inlineStr"/>
+      <c r="X355" t="inlineStr"/>
+      <c r="Y355" t="inlineStr"/>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2026073106545286.0</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>20</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
+      <c r="O356" t="inlineStr"/>
+      <c r="P356" t="inlineStr"/>
+      <c r="Q356" t="inlineStr"/>
+      <c r="R356" t="inlineStr"/>
+      <c r="S356" t="inlineStr"/>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>SOLICITAÇÃO DE INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>SUCOL ATENDIMENTO</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr"/>
+      <c r="X356" t="inlineStr"/>
+      <c r="Y356" t="inlineStr"/>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2026080609404579.0</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>20</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr"/>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>VIAÇÃO GARCIA</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>CAMPINAS</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>Campinas</t>
+        </is>
+      </c>
+      <c r="P357" t="n">
+        <v>3509502</v>
+      </c>
+      <c r="Q357" t="inlineStr"/>
+      <c r="R357" t="inlineStr"/>
+      <c r="S357" t="inlineStr"/>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>SOLICITAÇÃO DE INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>SUCOL ATENDIMENTO</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr"/>
+      <c r="X357" t="inlineStr"/>
+      <c r="Y357" t="inlineStr"/>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2026081310450364.0</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>10</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr"/>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr"/>
+      <c r="L358" t="inlineStr"/>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr"/>
+      <c r="O358" t="inlineStr"/>
+      <c r="P358" t="inlineStr"/>
+      <c r="Q358" t="inlineStr"/>
+      <c r="R358" t="inlineStr"/>
+      <c r="S358" t="inlineStr"/>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>SOLICITAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>2026-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr"/>
+      <c r="X358" t="inlineStr"/>
+      <c r="Y358" t="inlineStr"/>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>CARTÃO DE VISTORIA</t>
+        </is>
+      </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2026081409090889.0</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>10</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr"/>
+      <c r="J359" t="inlineStr"/>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>JUNDIAI</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>Jundiaí</t>
+        </is>
+      </c>
+      <c r="P359" t="n">
+        <v>3525904</v>
+      </c>
+      <c r="Q359" t="inlineStr"/>
+      <c r="R359" t="inlineStr"/>
+      <c r="S359" t="inlineStr"/>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>CADASTRO/RENOVAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>2026-08-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr"/>
+      <c r="X359" t="inlineStr"/>
+      <c r="Y359" t="inlineStr"/>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>CARTÃO DE VISTORIA</t>
+        </is>
+      </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2026081721343023.0</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>10</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr"/>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
+      <c r="O360" t="inlineStr"/>
+      <c r="P360" t="inlineStr"/>
+      <c r="Q360" t="inlineStr"/>
+      <c r="R360" t="inlineStr"/>
+      <c r="S360" t="inlineStr"/>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>CADASTRO/RENOVAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>2026-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="W360" t="inlineStr"/>
+      <c r="X360" t="inlineStr"/>
+      <c r="Y360" t="inlineStr"/>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>CARTÃO DE VISTORIA</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2026081815242977.0</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>10</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr"/>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>CAMPINAS</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>Campinas</t>
+        </is>
+      </c>
+      <c r="P361" t="n">
+        <v>3509502</v>
+      </c>
+      <c r="Q361" t="inlineStr"/>
+      <c r="R361" t="inlineStr"/>
+      <c r="S361" t="inlineStr"/>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>CADASTRO/RENOVAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>2026-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="W361" t="inlineStr"/>
+      <c r="X361" t="inlineStr"/>
+      <c r="Y361" t="inlineStr"/>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>CARTÃO DE VISTORIA</t>
+        </is>
+      </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2026081914302770.0</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>10</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr"/>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>VIAÇÃO STENICO</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
+      <c r="O362" t="inlineStr"/>
+      <c r="P362" t="inlineStr"/>
+      <c r="Q362" t="inlineStr"/>
+      <c r="R362" t="inlineStr"/>
+      <c r="S362" t="inlineStr"/>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>CADASTRO/RENOVAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>2026-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr"/>
+      <c r="X362" t="inlineStr"/>
+      <c r="Y362" t="inlineStr"/>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>CARTÃO DE VISTORIA</t>
+        </is>
+      </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>ASSUNTO sem mapeamento: 'QUEBRA DE VEÍCULO'</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2026082110582744.0</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>10</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>13.245.713/0001-67</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>VIASOL</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>VIASOL TRANSPORTES RODOVIÁRIOS LTDA.</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr"/>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>LIMEIRA</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>Limeira</t>
+        </is>
+      </c>
+      <c r="P363" t="n">
+        <v>3526902</v>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>LEME</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>Leme</t>
+        </is>
+      </c>
+      <c r="S363" t="n">
+        <v>3526704</v>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>QUEBRA DE VEÍCULO</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>2026-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr"/>
+      <c r="X363" t="inlineStr"/>
+      <c r="Y363" t="inlineStr"/>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2026082410444432.0</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>20</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr"/>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>FERNANDO BENITEZ BEZERRA</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr"/>
+      <c r="O364" t="inlineStr"/>
+      <c r="P364" t="inlineStr"/>
+      <c r="Q364" t="inlineStr"/>
+      <c r="R364" t="inlineStr"/>
+      <c r="S364" t="inlineStr"/>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>CADASTRO/RENOVAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="W364" t="inlineStr"/>
+      <c r="X364" t="inlineStr"/>
+      <c r="Y364" t="inlineStr"/>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>ASSUNTO sem mapeamento: 'EMBARQUE E DESEMBARQUE FORA DO TERMINAL'</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2026082510574684.0</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>10</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr"/>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>VALINHOS</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>Valinhos</t>
+        </is>
+      </c>
+      <c r="P365" t="n">
+        <v>3556206</v>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>CAMPINAS</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>Campinas</t>
+        </is>
+      </c>
+      <c r="S365" t="n">
+        <v>3509502</v>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>EMBARQUE E DESEMBARQUE FORA DO TERMINAL</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>GFISC - FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>2026-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr"/>
+      <c r="X365" t="inlineStr"/>
+      <c r="Y365" t="inlineStr"/>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2026082116005418.0</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>20</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr"/>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>EMPRESA CARVAN</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>SÃO JOSE DOS CAMPOS</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>São José dos Campos</t>
+        </is>
+      </c>
+      <c r="P366" t="n">
+        <v>3549904</v>
+      </c>
+      <c r="Q366" t="inlineStr"/>
+      <c r="R366" t="inlineStr"/>
+      <c r="S366" t="inlineStr"/>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>PRESTAÇÃO DE SERVIÇO DA EMPRESA</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="W366" t="inlineStr"/>
+      <c r="X366" t="inlineStr"/>
+      <c r="Y366" t="inlineStr"/>
+      <c r="Z366" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2026082612045288.0</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>20</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr"/>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>PAULO TUR LOCADORA</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr"/>
+      <c r="O367" t="inlineStr"/>
+      <c r="P367" t="inlineStr"/>
+      <c r="Q367" t="inlineStr"/>
+      <c r="R367" t="inlineStr"/>
+      <c r="S367" t="inlineStr"/>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>CADASTRO/RENOVAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="W367" t="inlineStr"/>
+      <c r="X367" t="inlineStr"/>
+      <c r="Y367" t="inlineStr"/>
+      <c r="Z367" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2026082614162777.0</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>20</v>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr"/>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>GEDEAN MACIEL SILVESTRE</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr"/>
+      <c r="O368" t="inlineStr"/>
+      <c r="P368" t="inlineStr"/>
+      <c r="Q368" t="inlineStr"/>
+      <c r="R368" t="inlineStr"/>
+      <c r="S368" t="inlineStr"/>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>CADASTRO/RENOVAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="W368" t="inlineStr"/>
+      <c r="X368" t="inlineStr"/>
+      <c r="Y368" t="inlineStr"/>
+      <c r="Z368" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2026083116345233.0</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>10</v>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr"/>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>PAULO TUR LOCADORA</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr"/>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr"/>
+      <c r="O369" t="inlineStr"/>
+      <c r="P369" t="inlineStr"/>
+      <c r="Q369" t="inlineStr"/>
+      <c r="R369" t="inlineStr"/>
+      <c r="S369" t="inlineStr"/>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>CADASTRO/RENOVAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="W369" t="inlineStr"/>
+      <c r="X369" t="inlineStr"/>
+      <c r="Y369" t="inlineStr"/>
+      <c r="Z369" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2026091009243753.0</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>20</v>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr"/>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr"/>
+      <c r="L370" t="inlineStr"/>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr"/>
+      <c r="O370" t="inlineStr"/>
+      <c r="P370" t="inlineStr"/>
+      <c r="Q370" t="inlineStr"/>
+      <c r="R370" t="inlineStr"/>
+      <c r="S370" t="inlineStr"/>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>CADASTRO/RENOVAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="W370" t="inlineStr"/>
+      <c r="X370" t="inlineStr"/>
+      <c r="Y370" t="inlineStr"/>
+      <c r="Z370" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>ASSUNTO sem mapeamento: 'DENÚNCIA'</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>2026091410282040.0</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>10</v>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>06.922.869/0001-70</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>PASSARO MARROM</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>PASS TRANSPORTES E SERVICOS AMBIENTAIS LTDA</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="P371" t="n">
+        <v>3550308</v>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>CAMPOS DO JORDÃO</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>Campos do Jordão</t>
+        </is>
+      </c>
+      <c r="S371" t="n">
+        <v>3509700</v>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>DENÚNCIA</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>GFISC - FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="V371" t="inlineStr"/>
+      <c r="W371" t="inlineStr"/>
+      <c r="X371" t="inlineStr"/>
+      <c r="Y371" t="inlineStr"/>
+      <c r="Z371" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2026091513534265.0</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>10</v>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr"/>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr"/>
+      <c r="O372" t="inlineStr"/>
+      <c r="P372" t="inlineStr"/>
+      <c r="Q372" t="inlineStr"/>
+      <c r="R372" t="inlineStr"/>
+      <c r="S372" t="inlineStr"/>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>CADASTRO/RENOVAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>2026-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="W372" t="inlineStr"/>
+      <c r="X372" t="inlineStr"/>
+      <c r="Y372" t="inlineStr"/>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2026091707422934.0</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>10</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>20.336.241/0001-13</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>BUS+</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>CONSORCIO BUS +</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>BUS +</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>CAMPINAS - TERMINAL MAGALHAES TEIXEIRA</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>Campinas</t>
+        </is>
+      </c>
+      <c r="P373" t="n">
+        <v>3509502</v>
+      </c>
+      <c r="Q373" t="inlineStr"/>
+      <c r="R373" t="inlineStr"/>
+      <c r="S373" t="inlineStr"/>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>MUDANÇA DE TABELA DE HORÁRIO</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr"/>
+      <c r="W373" t="inlineStr"/>
+      <c r="X373" t="inlineStr"/>
+      <c r="Y373" t="inlineStr"/>
+      <c r="Z373" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2026091712595242.0</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>10</v>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr"/>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>GEDEAN MACIEL SILVESTRE</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>IPERO</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>Iperó</t>
+        </is>
+      </c>
+      <c r="P374" t="n">
+        <v>3521002</v>
+      </c>
+      <c r="Q374" t="inlineStr"/>
+      <c r="R374" t="inlineStr"/>
+      <c r="S374" t="inlineStr"/>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>CADASTRO/RENOVAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="W374" t="inlineStr"/>
+      <c r="X374" t="inlineStr"/>
+      <c r="Y374" t="inlineStr"/>
+      <c r="Z374" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2026091810355597.0</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>10</v>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>40.181.203/0001-46</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>ABC SISTEMA DE TRANSPORTE SPE S.A.</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>SAO BERNARDO DO CAMPO</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>São Bernardo do Campo</t>
+        </is>
+      </c>
+      <c r="P375" t="n">
+        <v>3548708</v>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>SAO PAULO - BERRINI</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="S375" t="n">
+        <v>3550308</v>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>INCLUSÃO DE NOVAS LINHAS</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr"/>
+      <c r="W375" t="inlineStr"/>
+      <c r="X375" t="inlineStr"/>
+      <c r="Y375" t="inlineStr"/>
+      <c r="Z375" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2026091812312371.0</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>10</v>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr"/>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>EMPRESA NENA</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="P376" t="n">
+        <v>3550308</v>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>FRANCA</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>Franca</t>
+        </is>
+      </c>
+      <c r="S376" t="n">
+        <v>3516200</v>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>APREENSÃO DE VEÍCULOS</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>GFISC - FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr"/>
+      <c r="W376" t="inlineStr"/>
+      <c r="X376" t="inlineStr"/>
+      <c r="Y376" t="inlineStr"/>
+      <c r="Z376" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>ASSUNTO sem mapeamento: 'DENÚNCIA'</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2026092106462092.0</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>10</v>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr"/>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>PRAIA GRANDE</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>Praia Grande</t>
+        </is>
+      </c>
+      <c r="P377" t="n">
+        <v>3541000</v>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>SAO VICENTE</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>São Vicente</t>
+        </is>
+      </c>
+      <c r="S377" t="n">
+        <v>3551009</v>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>DENÚNCIA</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>GFISC - FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr"/>
+      <c r="W377" t="inlineStr"/>
+      <c r="X377" t="inlineStr"/>
+      <c r="Y377" t="inlineStr"/>
+      <c r="Z377" t="inlineStr">
+        <is>
+          <t>MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2026092008112668.0</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>10</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr"/>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>USUARIO</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr"/>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>RIBEIRÃO PRETO</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>Ribeirão Preto</t>
+        </is>
+      </c>
+      <c r="P378" t="n">
+        <v>3543402</v>
+      </c>
+      <c r="Q378" t="inlineStr"/>
+      <c r="R378" t="inlineStr"/>
+      <c r="S378" t="inlineStr"/>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>SOLICITAÇÃO DE INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>GFISC - FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr"/>
+      <c r="W378" t="inlineStr"/>
+      <c r="X378" t="inlineStr"/>
+      <c r="Y378" t="inlineStr"/>
+      <c r="Z378" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2026092111075936.0</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>20</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr"/>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>VIAÇÃO GUERRINO</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr"/>
+      <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>BARRA FUNDA</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr"/>
+      <c r="P379" t="inlineStr"/>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>BIRIGUI</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>Birigui</t>
+        </is>
+      </c>
+      <c r="S379" t="n">
+        <v>3506508</v>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>PRESTAÇÃO DE SERVIÇO DA EMPRESA</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V379" t="inlineStr"/>
+      <c r="W379" t="inlineStr"/>
+      <c r="X379" t="inlineStr"/>
+      <c r="Y379" t="inlineStr"/>
+      <c r="Z379" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2026092109393845.0</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>20</v>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr"/>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>EMPRESA VIASOL</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr"/>
+      <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOGI MIRIM </t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>Mogi Mirim</t>
+        </is>
+      </c>
+      <c r="P380" t="n">
+        <v>3530805</v>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>LIMEIRA</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>Limeira</t>
+        </is>
+      </c>
+      <c r="S380" t="n">
+        <v>3526902</v>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>PRESTAÇÃO DE SERVIÇO DA EMPRESA</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr"/>
+      <c r="W380" t="inlineStr"/>
+      <c r="X380" t="inlineStr"/>
+      <c r="Y380" t="inlineStr"/>
+      <c r="Z380" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2026092119521426.0</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>10</v>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>40.181.203/0001-46</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>ABC SISTEMA DE TRANSPORTE SPE S.A.</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr"/>
+      <c r="N381" t="inlineStr"/>
+      <c r="O381" t="inlineStr"/>
+      <c r="P381" t="inlineStr"/>
+      <c r="Q381" t="inlineStr"/>
+      <c r="R381" t="inlineStr"/>
+      <c r="S381" t="inlineStr"/>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>PRESTAÇÃO DE SERVIÇO DA EMPRESA</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>GFISC - FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr"/>
+      <c r="W381" t="inlineStr"/>
+      <c r="X381" t="inlineStr"/>
+      <c r="Y381" t="inlineStr"/>
+      <c r="Z381" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2026092209370394.0</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>20</v>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>45.992.724/0001-05</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>RAPIDO LUXO CAMPINAS</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>RAPIDO LUXO CAMPINAS LTDA</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>RAPIDO CAMPINAS</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>301, 302 E 602</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>JUNDIAI</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>Jundiaí</t>
+        </is>
+      </c>
+      <c r="P382" t="n">
+        <v>3525904</v>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>CAJAMAR</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>Cajamar</t>
+        </is>
+      </c>
+      <c r="S382" t="n">
+        <v>3509205</v>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>MUDANÇA DE TABELA DE HORÁRIO</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr"/>
+      <c r="W382" t="inlineStr"/>
+      <c r="X382" t="inlineStr"/>
+      <c r="Y382" t="inlineStr"/>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2026092211022396.0</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>10</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>53.401.659/0001-16</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>CIDADE NATUREZA</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>CIDADE NATUREZA TRANSPORTES E TURISMO LTDA</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>TRANS-CINTER</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>5107 E 5109</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>SAO JOSE DOS CAMPOS</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>São José dos Campos</t>
+        </is>
+      </c>
+      <c r="P383" t="n">
+        <v>3549904</v>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>MONTEIRO LOBATO</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>Monteiro Lobato</t>
+        </is>
+      </c>
+      <c r="S383" t="n">
+        <v>3531704</v>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>MUDANÇA DE TABELA DE HORÁRIO</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V383" t="inlineStr"/>
+      <c r="W383" t="inlineStr"/>
+      <c r="X383" t="inlineStr"/>
+      <c r="Y383" t="inlineStr"/>
+      <c r="Z383" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2026092210441675.0</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>10</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr"/>
+      <c r="J384" t="inlineStr"/>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr"/>
+      <c r="N384" t="inlineStr"/>
+      <c r="O384" t="inlineStr"/>
+      <c r="P384" t="inlineStr"/>
+      <c r="Q384" t="inlineStr"/>
+      <c r="R384" t="inlineStr"/>
+      <c r="S384" t="inlineStr"/>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>CADASTRO/RENOVAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>2026-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="W384" t="inlineStr"/>
+      <c r="X384" t="inlineStr"/>
+      <c r="Y384" t="inlineStr"/>
+      <c r="Z384" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AB384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2026092308073678.0</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>10</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr"/>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>USUARIO</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr"/>
+      <c r="M385" t="inlineStr"/>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>CARAPICUIBA</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>Carapicuíba</t>
+        </is>
+      </c>
+      <c r="P385" t="n">
+        <v>3510609</v>
+      </c>
+      <c r="Q385" t="inlineStr"/>
+      <c r="R385" t="inlineStr"/>
+      <c r="S385" t="inlineStr"/>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>PRESTAÇÃO DE SERVIÇO DA EMPRESA</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr"/>
+      <c r="W385" t="inlineStr"/>
+      <c r="X385" t="inlineStr"/>
+      <c r="Y385" t="inlineStr"/>
+      <c r="Z385" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2026092323035269.0</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>10</v>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>40.181.203/0001-46</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>ABC SISTEMA DE TRANSPORTE SPE S.A.</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>SAO BERNARDO DO CAMPO</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>São Bernardo do Campo</t>
+        </is>
+      </c>
+      <c r="P386" t="n">
+        <v>3548708</v>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="S386" t="n">
+        <v>3550308</v>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>MUDANÇA DE TABELA DE HORÁRIO</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr"/>
+      <c r="W386" t="inlineStr"/>
+      <c r="X386" t="inlineStr"/>
+      <c r="Y386" t="inlineStr"/>
+      <c r="Z386" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2026092320462650.0</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>10</v>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>40.181.203/0001-46</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>ABC SISTEMA DE TRANSPORTE SPE S.A.</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>DIADEMA</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>Diadema</t>
+        </is>
+      </c>
+      <c r="P387" t="n">
+        <v>3513801</v>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="S387" t="n">
+        <v>3550308</v>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>AUMENTO DE FROTA</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V387" t="inlineStr"/>
+      <c r="W387" t="inlineStr"/>
+      <c r="X387" t="inlineStr"/>
+      <c r="Y387" t="inlineStr"/>
+      <c r="Z387" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Fretamento sem empresa (assunto não é transporte irregular/clandestino)</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2026092310585446.0</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>10</v>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="inlineStr"/>
+      <c r="L388" t="inlineStr"/>
+      <c r="M388" t="inlineStr"/>
+      <c r="N388" t="inlineStr"/>
+      <c r="O388" t="inlineStr"/>
+      <c r="P388" t="inlineStr"/>
+      <c r="Q388" t="inlineStr"/>
+      <c r="R388" t="inlineStr"/>
+      <c r="S388" t="inlineStr"/>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>CADASTRO/RENOVAÇÃO FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>GEREG - REGULATÓRIO</t>
+        </is>
+      </c>
+      <c r="V388" t="inlineStr"/>
+      <c r="W388" t="inlineStr"/>
+      <c r="X388" t="inlineStr"/>
+      <c r="Y388" t="inlineStr"/>
+      <c r="Z388" t="inlineStr">
+        <is>
+          <t>FRETAMENTO</t>
+        </is>
+      </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>2026092419533572.0</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>10</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr"/>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>SÃO BERNARDO DO CAMPO</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>São Bernardo do Campo</t>
+        </is>
+      </c>
+      <c r="P389" t="n">
+        <v>3548708</v>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>CUBATÃO</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>Cubatão</t>
+        </is>
+      </c>
+      <c r="S389" t="n">
+        <v>3513504</v>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>SUGESTÃO</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr"/>
+      <c r="W389" t="inlineStr"/>
+      <c r="X389" t="inlineStr"/>
+      <c r="Y389" t="inlineStr"/>
+      <c r="Z389" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2026092418564853.0</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>10</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>20.336.241/0001-13</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>BUS+</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>CONSORCIO BUS +</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>BUS +</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>697 E 703</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>HORTOLANDIA</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>Hortolândia</t>
+        </is>
+      </c>
+      <c r="P390" t="n">
+        <v>3519071</v>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>CAMPINAS</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>Campinas</t>
+        </is>
+      </c>
+      <c r="S390" t="n">
+        <v>3509502</v>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>ADIANTAMENTO/ATRASO DE VEÍCULO</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>GFISC - FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr"/>
+      <c r="W390" t="inlineStr"/>
+      <c r="X390" t="inlineStr"/>
+      <c r="Y390" t="inlineStr"/>
+      <c r="Z390" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2026092514071451.0</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>20</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>43.377.936/0001-49</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>JANDAIA</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>JANDAIA TRANSPORTES E TURISMO LTDA</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr"/>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>PRESIDENTE PRUDENTE</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>Presidente Prudente</t>
+        </is>
+      </c>
+      <c r="P391" t="n">
+        <v>3541406</v>
+      </c>
+      <c r="Q391" t="inlineStr"/>
+      <c r="R391" t="inlineStr"/>
+      <c r="S391" t="inlineStr"/>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>BENEFICIO DE ESTUDANTE</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V391" t="inlineStr"/>
+      <c r="W391" t="inlineStr"/>
+      <c r="X391" t="inlineStr"/>
+      <c r="Y391" t="inlineStr"/>
+      <c r="Z391" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>2026092510563246.0</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>20</v>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>54.360.623/0001-02</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>VIAÇÃO PIRACICABANA</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>VIAÇÃO PIRACICABANA S/A</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>PIRACICABANA</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr"/>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>SAO PAULO (TIETE)</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="P392" t="n">
+        <v>3550308</v>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>ARARAQUARA</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>Araraquara</t>
+        </is>
+      </c>
+      <c r="S392" t="n">
+        <v>3503208</v>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>COBRANÇA DE PASSAGEM</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V392" t="inlineStr"/>
+      <c r="W392" t="inlineStr"/>
+      <c r="X392" t="inlineStr"/>
+      <c r="Y392" t="inlineStr"/>
+      <c r="Z392" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>2026092518152965.0</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>10</v>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr"/>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr"/>
+      <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr"/>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>PIRAPORA DO BOM GESUS</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr"/>
+      <c r="P393" t="inlineStr"/>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>SANTANA DE PARNAIBA</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>Santana de Parnaíba</t>
+        </is>
+      </c>
+      <c r="S393" t="n">
+        <v>3547304</v>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>INCLUSÃO DE NOVAS LINHAS</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V393" t="inlineStr"/>
+      <c r="W393" t="inlineStr"/>
+      <c r="X393" t="inlineStr"/>
+      <c r="Y393" t="inlineStr"/>
+      <c r="Z393" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA393" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>2026092723514838.0</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>10</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>40.181.203/0001-46</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>ABC SISTEMA DE TRANSPORTE SPE S.A.</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>SAO BERNARDO DO CAMPO</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>São Bernardo do Campo</t>
+        </is>
+      </c>
+      <c r="P394" t="n">
+        <v>3548708</v>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="S394" t="n">
+        <v>3550308</v>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>MUDANÇA DE ITINERÁRIO</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>GFISC - FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr"/>
+      <c r="W394" t="inlineStr"/>
+      <c r="X394" t="inlineStr"/>
+      <c r="Y394" t="inlineStr"/>
+      <c r="Z394" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>2026092519501367.0</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>20</v>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>54.360.623/0001-02</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>VIÇÃO PIRACICABANA</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>VIAÇÃO PIRACICABANA S/A</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>PIRACICABANA</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>PIRACICABA</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>Piracicaba</t>
+        </is>
+      </c>
+      <c r="P395" t="n">
+        <v>3538709</v>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>AMERICANA</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>Americana</t>
+        </is>
+      </c>
+      <c r="S395" t="n">
+        <v>3501608</v>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>GRATUIDADE DE IDOSOS</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V395" t="inlineStr"/>
+      <c r="W395" t="inlineStr"/>
+      <c r="X395" t="inlineStr"/>
+      <c r="Y395" t="inlineStr"/>
+      <c r="Z395" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>2026092811574878.0</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>10</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>20.336.241/0001-13</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>BUS+</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>CONSORCIO BUS +</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>BUS +</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>ITATIBA</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>Itatiba</t>
+        </is>
+      </c>
+      <c r="P396" t="n">
+        <v>3523404</v>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>MORUNGABA</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>Morungaba</t>
+        </is>
+      </c>
+      <c r="S396" t="n">
+        <v>3532009</v>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>MUDANÇA DE TABELA DE HORÁRIO</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>GFISC - FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr"/>
+      <c r="W396" t="inlineStr"/>
+      <c r="X396" t="inlineStr"/>
+      <c r="Y396" t="inlineStr"/>
+      <c r="Z396" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>2026092114594757.0</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>10</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>40.181.203/0001-46</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>ABC SISTEMA DE TRANSPORTE SPE S.A.</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr"/>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>SAO BERNARDO DO CAMPO</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>São Bernardo do Campo</t>
+        </is>
+      </c>
+      <c r="P397" t="n">
+        <v>3548708</v>
+      </c>
+      <c r="Q397" t="inlineStr"/>
+      <c r="R397" t="inlineStr"/>
+      <c r="S397" t="inlineStr"/>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>ACESSIBILIDADE</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V397" t="inlineStr"/>
+      <c r="W397" t="inlineStr"/>
+      <c r="X397" t="inlineStr"/>
+      <c r="Y397" t="inlineStr"/>
+      <c r="Z397" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>ASSUNTO sem mapeamento: 'DENÚNCIA'</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>2026092923254285.0</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>10</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr"/>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>SOCICAM</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr"/>
+      <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr"/>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>SAO PAULO (JABAQUARA)</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="P398" t="n">
+        <v>3550308</v>
+      </c>
+      <c r="Q398" t="inlineStr"/>
+      <c r="R398" t="inlineStr"/>
+      <c r="S398" t="inlineStr"/>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>DENÚNCIA</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>GFISC - FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="V398" t="inlineStr"/>
+      <c r="W398" t="inlineStr"/>
+      <c r="X398" t="inlineStr"/>
+      <c r="Y398" t="inlineStr"/>
+      <c r="Z398" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>2026092919373658.0</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>10</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>20.336.241/0001-13</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>BUS+</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>CONSORCIO BUS +</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>BUS +</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>MONTE MOR</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>Monte Mor</t>
+        </is>
+      </c>
+      <c r="P399" t="n">
+        <v>3531803</v>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>INDAIATUBA</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>Indaiatuba</t>
+        </is>
+      </c>
+      <c r="S399" t="n">
+        <v>3520509</v>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>MÁ CONDIÇÃO DE VEÍCULO</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>GFISC - FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="V399" t="inlineStr"/>
+      <c r="W399" t="inlineStr"/>
+      <c r="X399" t="inlineStr"/>
+      <c r="Y399" t="inlineStr"/>
+      <c r="Z399" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA399" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2026092904510574.0</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>10</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>40.181.203/0001-46</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>ABC SISTEMA DE TRANSPORTE SPE S.A.</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>165 E 165EX1</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>RIBEIRÃO PIRES E RIO GRANDE DA SERRA</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>Ribeirão Pires</t>
+        </is>
+      </c>
+      <c r="P400" t="n">
+        <v>3543303</v>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>SÃO BERNARDO DO CAMPO</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>São Bernardo do Campo</t>
+        </is>
+      </c>
+      <c r="S400" t="n">
+        <v>3548708</v>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>MUDANÇA DE TABELA DE HORÁRIO</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V400" t="inlineStr"/>
+      <c r="W400" t="inlineStr"/>
+      <c r="X400" t="inlineStr"/>
+      <c r="Y400" t="inlineStr"/>
+      <c r="Z400" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA400" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2026093021565311.0</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>10</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>06.922.869/0001-70</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>PASSARO MARROM</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>PASS TRANSPORTES E SERVICOS AMBIENTAIS LTDA</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>5506</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>UBATUBA</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>Ubatuba</t>
+        </is>
+      </c>
+      <c r="P401" t="n">
+        <v>3555406</v>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>CARAGUATATUBA</t>
+        </is>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>Caraguatatuba</t>
+        </is>
+      </c>
+      <c r="S401" t="n">
+        <v>3510500</v>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>MUDANÇA DE TABELA DE HORÁRIO</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V401" t="inlineStr"/>
+      <c r="W401" t="inlineStr"/>
+      <c r="X401" t="inlineStr"/>
+      <c r="Y401" t="inlineStr"/>
+      <c r="Z401" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA401" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2026093022553460.0</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>10</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr"/>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>USUARIO</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr"/>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>SÃO PAULO (TIETE)</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="P402" t="n">
+        <v>3550308</v>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>INDAIATUBA</t>
+        </is>
+      </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>Indaiatuba</t>
+        </is>
+      </c>
+      <c r="S402" t="n">
+        <v>3520509</v>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAGAGEM </t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr"/>
+      <c r="W402" t="inlineStr"/>
+      <c r="X402" t="inlineStr"/>
+      <c r="Y402" t="inlineStr"/>
+      <c r="Z402" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA402" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2026100107174034.0</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>10</v>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr"/>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>USUARIO</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr"/>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>DIADEMA</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>Diadema</t>
+        </is>
+      </c>
+      <c r="P403" t="n">
+        <v>3513801</v>
+      </c>
+      <c r="Q403" t="inlineStr"/>
+      <c r="R403" t="inlineStr"/>
+      <c r="S403" t="inlineStr"/>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>ACESSIBILIDADE</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V403" t="inlineStr"/>
+      <c r="W403" t="inlineStr"/>
+      <c r="X403" t="inlineStr"/>
+      <c r="Y403" t="inlineStr"/>
+      <c r="Z403" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA403" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2026093015364884.0</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>10</v>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr"/>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>GUARULHOS</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>Guarulhos</t>
+        </is>
+      </c>
+      <c r="P404" t="n">
+        <v>3518800</v>
+      </c>
+      <c r="Q404" t="inlineStr"/>
+      <c r="R404" t="inlineStr"/>
+      <c r="S404" t="inlineStr"/>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>TRANSPORTE CLANDESTINO</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>GFISC - FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="V404" t="inlineStr"/>
+      <c r="W404" t="inlineStr"/>
+      <c r="X404" t="inlineStr"/>
+      <c r="Y404" t="inlineStr"/>
+      <c r="Z404" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA404" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2026093008111646.0</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>10</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr"/>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>USUARIO</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>SANTOS</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="P405" t="n">
+        <v>3548500</v>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>ITANHAEM</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>Itanhaém</t>
+        </is>
+      </c>
+      <c r="S405" t="n">
+        <v>3522109</v>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>SOLICITAÇÃO DE INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V405" t="inlineStr"/>
+      <c r="W405" t="inlineStr"/>
+      <c r="X405" t="inlineStr"/>
+      <c r="Y405" t="inlineStr"/>
+      <c r="Z405" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA405" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>2026100119115375.0</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>10</v>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>06.922.869/0001-70</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>PASSARO MARROM</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>PASS TRANSPORTES E SERVICOS AMBIENTAIS LTDA</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr"/>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>SÃO PAULO (TIETE)</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="P406" t="n">
+        <v>3550308</v>
+      </c>
+      <c r="Q406" t="inlineStr"/>
+      <c r="R406" t="inlineStr"/>
+      <c r="S406" t="inlineStr"/>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAGAGEM </t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V406" t="inlineStr"/>
+      <c r="W406" t="inlineStr"/>
+      <c r="X406" t="inlineStr"/>
+      <c r="Y406" t="inlineStr"/>
+      <c r="Z406" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA406" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>2026092217222953.0</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>10</v>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>40.181.203/0001-46</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>ABC SISTEMA DE TRANSPORTE SPE S.A.</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>NEXTMOBILIDADE</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>DIADEMA</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>Diadema</t>
+        </is>
+      </c>
+      <c r="P407" t="n">
+        <v>3513801</v>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="S407" t="n">
+        <v>3550308</v>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>AUMENTO DE FROTA</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>GFISC - FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="V407" t="inlineStr"/>
+      <c r="W407" t="inlineStr"/>
+      <c r="X407" t="inlineStr"/>
+      <c r="Y407" t="inlineStr"/>
+      <c r="Z407" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2026092812221319.0</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>10</v>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>06.922.869/0001-70</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>PASSARO MARROM</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>PASS TRANSPORTES E SERVICOS AMBIENTAIS LTDA</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr"/>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>SANTOS</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="P408" t="n">
+        <v>3548500</v>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>SAO SEBASTIÃO</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>São Sebastião</t>
+        </is>
+      </c>
+      <c r="S408" t="n">
+        <v>3550704</v>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>BILHETE DE PASSAGEM</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr"/>
+      <c r="W408" t="inlineStr"/>
+      <c r="X408" t="inlineStr"/>
+      <c r="Y408" t="inlineStr"/>
+      <c r="Z408" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>2026093009170992.0</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>10</v>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr"/>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>LBV BOA VONTADE</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr"/>
+      <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>MOGI DAS CRUZES</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>Mogi das Cruzes</t>
+        </is>
+      </c>
+      <c r="P409" t="n">
+        <v>3530607</v>
+      </c>
+      <c r="Q409" t="inlineStr"/>
+      <c r="R409" t="inlineStr"/>
+      <c r="S409" t="inlineStr"/>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>SOLICITAÇÃO DE INFORMAÇÃO</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr"/>
+      <c r="W409" t="inlineStr"/>
+      <c r="X409" t="inlineStr"/>
+      <c r="Y409" t="inlineStr"/>
+      <c r="Z409" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>2026092118384366.0</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>10</v>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>61.084.018/0001-03</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>VIAÇÃO COMETA</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>VIAÇÃO COMETA S/A</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>COMETA</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>RIBEIRÃO PRETO</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>Ribeirão Preto</t>
+        </is>
+      </c>
+      <c r="P410" t="n">
+        <v>3543402</v>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>FRANCA</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>Franca</t>
+        </is>
+      </c>
+      <c r="S410" t="n">
+        <v>3516200</v>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>MUDANÇA DE TABELA DE HORÁRIO</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V410" t="inlineStr"/>
+      <c r="W410" t="inlineStr"/>
+      <c r="X410" t="inlineStr"/>
+      <c r="Y410" t="inlineStr"/>
+      <c r="Z410" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA410" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>ASSUNTO sem mapeamento: 'CARTEIRA DEFICIENTES'</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>2026100211340443.0</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>10</v>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>61.084.018/0001-03</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>VIAÇÃO COMETA E VALE DO TIETE</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>VIAÇÃO COMETA S/A</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>COMETA</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr"/>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>JUNDIAI</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>Jundiaí</t>
+        </is>
+      </c>
+      <c r="P411" t="n">
+        <v>3525904</v>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>SÃO PAULO</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="S411" t="n">
+        <v>3550308</v>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>CARTEIRA DEFICIENTES</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V411" t="inlineStr"/>
+      <c r="W411" t="inlineStr"/>
+      <c r="X411" t="inlineStr"/>
+      <c r="Y411" t="inlineStr"/>
+      <c r="Z411" t="inlineStr">
+        <is>
+          <t>INTERMUNICIPAL</t>
+        </is>
+      </c>
+      <c r="AA411" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>2026100216144364.0</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>10</v>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>08.325.415/0001-47</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>UNILESTE</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>CONSÓRCIO UNILESTE</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>UNILESTE</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>POÁ</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>Poá</t>
+        </is>
+      </c>
+      <c r="P412" t="n">
+        <v>3539806</v>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>SÃO PALO</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr"/>
+      <c r="S412" t="inlineStr"/>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>SUGESTÃO</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr"/>
+      <c r="W412" t="inlineStr"/>
+      <c r="X412" t="inlineStr"/>
+      <c r="Y412" t="inlineStr"/>
+      <c r="Z412" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA412" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>DATA R. vazia e STATUS='vazio' — expurgado</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026100122392270.0</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>10</v>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr"/>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>USUÁRIO</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>MAUA</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>Mauá</t>
+        </is>
+      </c>
+      <c r="P413" t="n">
+        <v>3529401</v>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>SANTO ANDRE</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>Santo André</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>3547809</v>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>INCLUSÃO DE NOVAS LINHAS</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>GPLAN - PLANEJAMENTO</t>
+        </is>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" t="inlineStr"/>
+      <c r="X413" t="inlineStr"/>
+      <c r="Y413" t="inlineStr"/>
+      <c r="Z413" t="inlineStr">
+        <is>
+          <t>METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="AB413" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
